--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -21,7 +21,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -71,8 +71,12 @@
       <b val="1"/>
       <sz val="12"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -103,6 +107,12 @@
         <bgColor rgb="00FDE2E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+        <bgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -130,7 +140,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -177,6 +187,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -576,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -592,10 +606,8 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
+      <c r="D5" s="4" t="n">
+        <v>1</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1321,15 +1333,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I4" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I4" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J4" s="16" t="inlineStr"/>
       <c r="K4" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-03 (sprint: Workflow as Engine). The single most important schema change of the sprint — everything downstream (engine, side-effects, joined UI) reads this shape.</t>
+          <t>Imported from Epic 1 WE-03 (sprint: Workflow as Engine). The single most important schema change of the sprint — everything downstream (engine, side-effects, joined UI) reads this shape. | Shipped 2026-08-16 (commit follows). Migration stage_objects_extend_v1 applied to 2/2 tenants. 7/7 pytest in tests/test_we03_stage_objects.py.</t>
         </is>
       </c>
       <c r="L4" s="16" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1225,15 +1225,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I2" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I2" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J2" s="16" t="inlineStr"/>
       <c r="K2" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-01 (sprint: Workflow as Engine). Foundational — unlocks WE-06..WE-09 (the engine needs to read these). See Spec deck slide 9 (data model table).</t>
+          <t>Imported from Epic 1 WE-01 (sprint: Workflow as Engine). Foundational — unlocks WE-06..WE-09 (the engine needs to read these). See Spec deck slide 9 (data model table). | Shipped 2026-08-16 (commit follows). Migration backfill_task_workflow_link_v1 applied (scanned=10, matched=1). 6 pytest + 11 integration scenarios green. Compound index tasks_tenant_workflow_stage created.</t>
         </is>
       </c>
       <c r="L2" s="16" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1279,15 +1279,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I3" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I3" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J3" s="18" t="inlineStr"/>
       <c r="K3" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-02 (sprint: Workflow as Engine). Enables WE-04 Settings redesign. Idempotent via migration ledger.</t>
+          <t>Imported from Epic 1 WE-02 (sprint: Workflow as Engine). Enables WE-04 Settings redesign. Idempotent via migration ledger. | Shipped 2026-08-16 (commit follows). Migration drop_ghost_workflow_collections_v1 applied (workflow_templates unset on 1 tenant, lexicon.workflows unset on 2 tenants). Backend: removed writes in auth.py + onboarding.py + DEFAULT_LEXICON.workflows + _bp_workflows + os_summary count. Frontend: removed lex() merge + BusinessVocabulary Workflow Pipelines section + CompanyDetails Workflows editor. Legacy client PATCH still returns 200 (silent-drop). Updated tests test_iteration44 + test_iteration45; existing WE-01 + WE-03 pytest still 13/13 green.</t>
         </is>
       </c>
       <c r="L3" s="18" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1387,15 +1387,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I5" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J5" s="18" t="inlineStr"/>
       <c r="K5" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-04 (sprint: Workflow as Engine). Depends on WE-03 (stage-object shape). See Spec deck slide 12.</t>
+          <t>Imported from Epic 1 WE-04 (sprint: Workflow as Engine). Depends on WE-03 (stage-object shape). See Spec deck slide 12. | Shipped 2026-08-16 (commit follows). Settings.js is now a 4-tab layout: Business / Operations / Money / Account. OperatingModelEditor extended with inline stage task templates (title + role + evidence_required), stage approval gate (role dropdown + required toggle), and read-only side-effect chips. Verified E2E in browser as Kapoor Cotton Mills owner: all 4 tabs render + activate; added a task template + set approval on the Production pipeline, saved, DB round-trip confirmed via direct query.</t>
         </is>
       </c>
       <c r="L5" s="18" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -866,6 +866,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -890,6 +891,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -904,6 +906,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="130" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
@@ -919,6 +922,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -926,6 +930,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
@@ -941,7 +946,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Backlog (kickoff)</t>
+          <t>COMPLETE (WE-05 gate passed 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -1441,15 +1446,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I6" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J6" s="16" t="inlineStr"/>
       <c r="K6" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-05 (sprint: Workflow as Engine). See Testing Plan deck slide 4 (Phase 1 exit gate).</t>
+          <t>Imported from Epic 1 WE-05 (sprint: Workflow as Engine). See Testing Plan deck slide 4 (Phase 1 exit gate). | PASSED 2026-08-16. Gate results: (1) 71/71 targeted regression pytest green (WE-01 + WE-03 + operating_model + lexicon + workflow_finance_link + workflows_dynamic + migrations_ledger). (2) All 3 Sprint 1 migrations idempotent on second boot -- no 'Migration applied' log lines, ledger has exactly one row per migration with original applied_at timestamps. (3) Ghost collections stay gone: 0 tenants with workflow_templates, 0 with lexicon.workflows. (4) WE-03 stage extension holds: 44 stages have all 3 new fields (tasks[], approval, side_effects[]), 0 missing. (5) All 4 indexes present (tasks compound + billing/crm/invoices audit indexes). (6) Workflows page for Kapoor Cotton Mills renders 2 cards, 4 stage columns, 3 pipeline tabs -- zero behaviour diff for existing tenants. (7) 4-tab Settings functional (verified in WE-04). Backend /api/health 200 post-restart.</t>
         </is>
       </c>
       <c r="L6" s="16" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -974,6 +974,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
@@ -989,7 +990,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Backlog (kickoff)</t>
+          <t>COMPLETE (WE-10 gate passed 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -1500,15 +1501,15 @@
           <t>L</t>
         </is>
       </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J7" s="18" t="inlineStr"/>
       <c r="K7" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-06 (sprint: Workflow as Engine). The core of the sprint. See Spec deck slide 10 (function table).</t>
+          <t>Imported from Epic 1 WE-06 (sprint: Workflow as Engine). The core of the sprint. See Spec deck slide 10 (function table). | Shipped 2026-08-16. services/workflow_engine.py with on_stage_enter + check_stage_ready + advance. 13/13 engine scenarios PASS (task-open refusal, ready-then-succeed, override+reason, override-missing-reason, atomic CAS race, on-enter idempotent, side-effect idempotent, notify no-recipients, approval gate, approval role check, terminal completed_at, skip-stage rejected, registered kinds).</t>
         </is>
       </c>
       <c r="L7" s="18" t="inlineStr">
@@ -1554,15 +1555,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J8" s="16" t="inlineStr"/>
       <c r="K8" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-07 (sprint: Workflow as Engine). Prevents regression forever — future refactors that add a stray workflows.update_one({stage:...}) fail the contract test at CI.</t>
+          <t>Imported from Epic 1 WE-07 (sprint: Workflow as Engine). Prevents regression forever — future refactors that add a stray workflows.update_one({stage:...}) fail the contract test at CI. | Shipped 2026-08-16. advance_workflow endpoint + decisions.approve auto-advance both delegate through engine.advance. tests/test_we07_single_writer_contract.py greenlists services/workflow_engine.py + server.py initial-insert sites only; grep-scan fails CI if any other file mutates workflows.stage.</t>
         </is>
       </c>
       <c r="L8" s="16" t="inlineStr">
@@ -1608,15 +1609,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J9" s="18" t="inlineStr"/>
       <c r="K9" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-08 (sprint: Workflow as Engine). Migrates the FIX-001-B pattern from bespoke advance_workflow code into a first-class engine capability. Every future 'when stage X, do Y' request land</t>
+          <t>Imported from Epic 1 WE-08 (sprint: Workflow as Engine). Migrates the FIX-001-B pattern from bespoke advance_workflow code into a first-class engine capability. Every future 'when stage X, do Y' request land | Shipped 2026-08-16. Side-effects registry with create_expense + notify_role kinds. FIX-001-B ported into _side_effect_create_expense (idempotent per workflow_id). Migration backfill_procurement_side_effect_v1 bound the create_expense kind to every existing procurement pipeline's terminal stage (scanned=2, touched=2). Zero behaviour diff for existing tenants.</t>
         </is>
       </c>
       <c r="L9" s="18" t="inlineStr">
@@ -1662,15 +1663,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J10" s="16" t="inlineStr"/>
       <c r="K10" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-09 (sprint: Workflow as Engine). Prevents the two hardest-to-diagnose classes of workflow bugs. Regression tests in Testing Plan deck slide 6.</t>
+          <t>Imported from Epic 1 WE-09 (sprint: Workflow as Engine). Prevents the two hardest-to-diagnose classes of workflow bugs. Regression tests in Testing Plan deck slide 6. | Shipped 2026-08-16. workflows.stage_version optimistic-lock counter. engine.advance uses find_one_and_update on (id, stage_version, current_stage) so concurrent writers race safely -- exactly one wins, the other exits with already_advanced=True. Migration backfill_stage_version_v1 initialised 13 workflows to stage_version=0. Verified live via scenario 5 (asyncio.gather of two advances -&gt; 1 winner + 1 loser).</t>
         </is>
       </c>
       <c r="L10" s="16" t="inlineStr">
@@ -1716,15 +1717,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I11" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J11" s="18" t="inlineStr"/>
       <c r="K11" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-10 (sprint: Workflow as Engine). See Testing Plan deck slides 5-7 (Phase 2 core + guarantees + stage-object migration).</t>
+          <t>Imported from Epic 1 WE-10 (sprint: Workflow as Engine). See Testing Plan deck slides 5-7 (Phase 2 core + guarantees + stage-object migration). | PASSED 2026-08-16. Sprint 2 exit gate: (a) engine unit scenarios 13/13 PASS. (b) Single-writer contract 2/2 tests PASS. (c) Regression: WE-01 + WE-03 + workflows_dynamic + workflow_finance_link + migrations_ledger = 72/72 PASS (2 iteration-test errors are pre-existing env issues, missing REACT_APP_BACKEND_URL). (d) Browser zero-diff: /my-work?view=workflows still shows 2 cards + 4 stage columns + 3 pipeline tabs for Kapoor Cotton Mills. (e) Both Sprint 2 migrations applied cleanly on live DB (touched 2 tenants + 13 workflows).</t>
         </is>
       </c>
       <c r="L11" s="18" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1018,6 +1018,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -1033,7 +1034,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Backlog (kickoff)</t>
+          <t>COMPLETE (WE-11..14 shipped 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -1771,15 +1772,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I12" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J12" s="16" t="inlineStr"/>
       <c r="K12" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-11 (sprint: Workflow as Engine). See Spec deck slide 13 (My Work + Workflow, joined).</t>
+          <t>Imported from Epic 1 WE-11 (sprint: Workflow as Engine). See Spec deck slide 13 (My Work + Workflow, joined). | Shipped 2026-08-16. MyWork TaskCard renders 'stage chip' (workflow title + current stage) for every task with workflow_id. Backend enrich_tasks batch-fetches workflow_summary per task in one query. Ad-hoc tasks (no workflow_id) render no chip -- behaviour unchanged. Verified via API: 1/17 tasks linked, chip payload includes id/type/title/stage/short_id.</t>
         </is>
       </c>
       <c r="L12" s="16" t="inlineStr">
@@ -1825,15 +1826,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J13" s="18" t="inlineStr"/>
       <c r="K13" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-12 (sprint: Workflow as Engine). The other half of WE-11 — from the workflow-board side.</t>
+          <t>Imported from Epic 1 WE-12 (sprint: Workflow as Engine). The other half of WE-11 — from the workflow-board side. | Shipped 2026-08-16. Workflow card renders inline task list (title + assignee initial avatar) for OPEN tasks at the card's current stage. Backend GET /workflows?with_tasks=true batch-fetches stage_tasks[] per card in a single $or query. Verified live on Kapoor Procurement pipeline: 'Supplier payment to Rajesh Cotton Traders' card at 'requested' shows the finance-assigned task inline with a 'PS' avatar chip.</t>
         </is>
       </c>
       <c r="L13" s="18" t="inlineStr">
@@ -1879,15 +1880,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I14" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I14" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J14" s="16" t="inlineStr"/>
       <c r="K14" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-13 (sprint: Workflow as Engine). Pairs with WE-07 (single-writer contract). The override IS allowed — but never invisible.</t>
+          <t>Imported from Epic 1 WE-13 (sprint: Workflow as Engine). Pairs with WE-07 (single-writer contract). The override IS allowed — but never invisible. | Shipped 2026-08-16. OverrideReasonDialog opens when engine.advance returns 409 (check_stage_ready False). Shows workflow title + engine's precise blocked reason (e.g. '1 task(s) still open at this stage'). Override button disabled until reason is entered. On confirm, calls advance with override=true + reason -- lands in wf.history + audit_log per WE-07. Verified live on Kapoor Procurement card: click Advance -&gt; dialog opened with correct reason text.</t>
         </is>
       </c>
       <c r="L14" s="16" t="inlineStr">
@@ -1933,15 +1934,15 @@
           <t>S</t>
         </is>
       </c>
-      <c r="I15" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I15" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J15" s="18" t="inlineStr"/>
       <c r="K15" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-14 (sprint: Workflow as Engine). Trivial cleanup — but leaving it in would confuse users about which surface is authoritative.</t>
+          <t>Imported from Epic 1 WE-14 (sprint: Workflow as Engine). Trivial cleanup — but leaving it in would confuse users about which surface is authoritative. | Shipped 2026-08-16. Board sub-tab retired -- MyWork ?view=workflows now goes straight to the Workflows pipeline board (which carries inline tasks per WE-12). TaskBoard import removed from MyWork; wfTab state removed; ?wf_tab=board deep links land on pipelines view silently.</t>
         </is>
       </c>
       <c r="L15" s="18" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -1062,6 +1062,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -1077,7 +1078,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Backlog (kickoff)</t>
+          <t>COMPLETE (WE-15/16 shipped 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -1988,15 +1989,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I16" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I16" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J16" s="16" t="inlineStr"/>
       <c r="K16" s="16" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-15 (sprint: Workflow as Engine). This is THE test that proves the sprint delivered. See Testing Plan deck slide 9 (Kapoor golden path). Adds ~15-20 assertions.</t>
+          <t>Imported from Epic 1 WE-15 (sprint: Workflow as Engine). This is THE test that proves the sprint delivered. See Testing Plan deck slide 9 (Kapoor golden path). Adds ~15-20 assertions. | Shipped 2026-08-16. Kapoor / Delhi Retail golden path codified in scripts/we15_golden_path_kapoor.py. Golden path (6 steps: order_received -&gt; Confirm-with-customer spawned -&gt; Sales closes -&gt; auto-advance to Confirmed -&gt; Prepare-invoice spawned to Finance -&gt; Finance closes -&gt; auto-advance to In Production -&gt; Pack+label spawned to Operations -&gt; Ops closes -&gt; auto-advance to Ready (terminal) -&gt; create_expense side-effect fires) PASSES. Negative case (task incomplete -&gt; check_stage_ready blocks, advance() raises 409 not_ready, workflow stays put) PASSES. Zero manual clicks in the full 3-stage chain. 15 assertions total.</t>
         </is>
       </c>
       <c r="L16" s="16" t="inlineStr">
@@ -2042,15 +2043,15 @@
           <t>M</t>
         </is>
       </c>
-      <c r="I17" s="17" t="inlineStr">
-        <is>
-          <t>Backlog</t>
+      <c r="I17" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
         </is>
       </c>
       <c r="J17" s="18" t="inlineStr"/>
       <c r="K17" s="18" t="inlineStr">
         <is>
-          <t>Imported from Epic 1 WE-16 (sprint: Workflow as Engine). See Testing Plan deck slide 10 (regression + back-compat) and slide 11 (per-phase exit gates).</t>
+          <t>Imported from Epic 1 WE-16 (sprint: Workflow as Engine). See Testing Plan deck slide 10 (regression + back-compat) and slide 11 (per-phase exit gates). | Shipped 2026-08-16. docs/WORKFLOW_ENGINE_ROLLBACK.md documents all 5 migrations (stage_objects_extend_v1, backfill_task_workflow_link_v1, drop_ghost_workflow_collections_v1, backfill_procurement_side_effect_v1, backfill_stage_version_v1) with revert query + post-revert check + blast radius per entry. Per-phase regression cheatsheet + migration ledger commands included. Final regression run: 73/73 pytest pass across all WE tests + workflow_finance_link + workflows_dynamic + migrations_ledger.</t>
         </is>
       </c>
       <c r="L17" s="18" t="inlineStr">

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -607,7 +607,7 @@
         </is>
       </c>
       <c r="D5" s="4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -866,7 +866,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -891,7 +890,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -906,7 +904,6 @@
         </is>
       </c>
     </row>
-    <row r="9"/>
     <row r="10" ht="130" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
@@ -922,7 +919,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -930,7 +926,6 @@
         </is>
       </c>
     </row>
-    <row r="13"/>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
@@ -974,7 +969,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
@@ -1018,7 +1012,6 @@
         </is>
       </c>
     </row>
-    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -1062,7 +1055,6 @@
         </is>
       </c>
     </row>
-    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -1117,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2057,6 +2049,66 @@
       <c r="L17" s="18" t="inlineStr">
         <is>
           <t>Epic 1 split 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>WE-01.5</t>
+        </is>
+      </c>
+      <c r="B18" s="16" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C18" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="16" t="inlineStr">
+        <is>
+          <t>Data model (Phase 1) — fix</t>
+        </is>
+      </c>
+      <c r="E18" s="16" t="inlineStr">
+        <is>
+          <t>Route voice-created tasks to their ROLE-owned stage (not initial stage)</t>
+        </is>
+      </c>
+      <c r="F18" s="16" t="inlineStr">
+        <is>
+          <t>Founder-surfaced gap: voice capture creates decision + workflow + N tasks, but the WE-01 post-pass tagged ALL tasks with the workflow's initial stage_key -- so engine could auto-advance ONCE then stall. Fix: each task is routed to the stage its role naturally owns (sales-&gt;order_received, finance-&gt;confirmed, ops-&gt;in_production, owner-&gt;approval_stage). Ships: stage.role field on WE-03 schema (AI can emit, backfill fills from tasks[0].role or legacy map), stage_owned_by() resolver in services/workflows.py, voice-capture post-pass update, backfill_stage_role_v1 migration, AI prompt update to emit role per stage. Multi-decision E2E: 6/6 scenarios PASS (Kapoor sales full chain / procurement w/ approval / single-task / role-no-match fallback / same-role dupes / resolver unit tests).</t>
+        </is>
+      </c>
+      <c r="G18" s="16" t="inlineStr">
+        <is>
+          <t>P1</t>
+        </is>
+      </c>
+      <c r="H18" s="16" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
+      <c r="I18" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J18" s="16" t="inlineStr">
+        <is>
+          <t>WE-01, WE-03, WE-06</t>
+        </is>
+      </c>
+      <c r="K18" s="16" t="inlineStr">
+        <is>
+          <t>Shipped 2026-08-16. Backfill scanned=2, touched=2 tenants. Live check: Kapoor's 3 pipelines all have stage.role populated (sales/finance/ops/production/owner). 73/73 pytest green after fix. All 6 role-routing E2E scenarios pass including approval-gate walkthrough.</t>
+        </is>
+      </c>
+      <c r="L18" s="16" t="inlineStr">
+        <is>
+          <t>Founder review 2026-08-16</t>
         </is>
       </c>
     </row>

--- a/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
+++ b/docs/DecisionOS_Epic5_Workflow_Engine.xlsx
@@ -585,11 +585,10 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>Epic 5 progress: 0 of 16 items Done  (0%)</t>
-        </is>
-      </c>
-    </row>
-    <row r="4"/>
+          <t>Epic 5 progress: 18 of 18 items Done  (100.0%)</t>
+        </is>
+      </c>
+    </row>
     <row r="5" ht="26" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
@@ -606,8 +605,10 @@
           <t>Done</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>17</v>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
@@ -637,19 +638,19 @@
         </is>
       </c>
       <c r="C6" s="6" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G6" s="7" t="inlineStr">
@@ -670,19 +671,19 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D7" s="9" t="n">
         <v>5</v>
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F7" s="8" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G7" s="10" t="inlineStr">
@@ -703,19 +704,19 @@
         </is>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="6" t="n">
         <v>4</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F8" s="8" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G8" s="7" t="inlineStr">
@@ -736,19 +737,19 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="F9" s="8" t="inlineStr">
         <is>
-          <t>Backlog</t>
+          <t>COMPLETE</t>
         </is>
       </c>
       <c r="G9" s="10" t="inlineStr">
@@ -866,6 +867,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
@@ -890,6 +892,7 @@
         </is>
       </c>
     </row>
+    <row r="6"/>
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
@@ -904,6 +907,7 @@
         </is>
       </c>
     </row>
+    <row r="9"/>
     <row r="10" ht="130" customHeight="1">
       <c r="A10" s="14" t="inlineStr">
         <is>
@@ -919,6 +923,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
@@ -926,6 +931,7 @@
         </is>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">
         <is>
@@ -953,7 +959,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>WE-01, WE-02, WE-03, WE-04, WE-05</t>
+          <t>WE-01, WE-02, WE-03, WE-04, WE-05, WE-01.5</t>
         </is>
       </c>
     </row>
@@ -969,6 +975,7 @@
         </is>
       </c>
     </row>
+    <row r="18"/>
     <row r="19">
       <c r="A19" s="15" t="inlineStr">
         <is>
@@ -1012,6 +1019,7 @@
         </is>
       </c>
     </row>
+    <row r="23"/>
     <row r="24">
       <c r="A24" s="15" t="inlineStr">
         <is>
@@ -1055,6 +1063,7 @@
         </is>
       </c>
     </row>
+    <row r="28"/>
     <row r="29">
       <c r="A29" s="15" t="inlineStr">
         <is>
@@ -1082,7 +1091,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>WE-15, WE-16</t>
+          <t>WE-15, WE-16, WE-EPIC5-BUG-3</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L18"/>
+  <dimension ref="A1:L19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -2109,6 +2118,66 @@
       <c r="L18" s="16" t="inlineStr">
         <is>
           <t>Founder review 2026-08-16</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="inlineStr">
+        <is>
+          <t>WE-EPIC5-BUG-3</t>
+        </is>
+      </c>
+      <c r="B19" s="18" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="n">
+        <v>4</v>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Sprint 4 defect — engine atomicity</t>
+        </is>
+      </c>
+      <c r="E19" s="18" t="inlineStr">
+        <is>
+          <t>Voice + manual workflow inserts must set stage_version=0 at insert time</t>
+        </is>
+      </c>
+      <c r="F19" s="18" t="inlineStr">
+        <is>
+          <t>Live Tracole browser E2E surfaced this: voice-created Decision B procurement workflow had `stage_version: None` in Mongo (only the WE-09 backfill migration set it, and only for pre-existing docs). Downstream WE-06.5 task-close hook called engine.advance -&gt; CAS filter used prev_version=int(None or 0)=0 vs Mongo's actual None -&gt; filter missed -&gt; workflow silently didn't advance. WE-EPIC5-BUG-2 widened the filter to {$in:[0,None]} (defense-in-depth for legacy docs), but the correct fix is at insert. Fixed both `_create_workflows` (voice) and `POST /workflows` (manual) inserts to include `stage_version: 0`. Added regression pytest guard (test_we_stage_version_init.py) that greps both insert dicts for the field so any future refactor can't silently reintroduce the gap. Verified live: healed Decision B workflow advanced cleanly requested-&gt;approved (version 0-&gt;1), fresh insert-path confirmed stage_version=0, approval-gate role rules still enforced.</t>
+        </is>
+      </c>
+      <c r="G19" s="18" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="H19" s="18" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="I19" s="19" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="J19" s="18" t="inlineStr">
+        <is>
+          <t>WE-06, WE-09, WE-EPIC5-BUG-2</t>
+        </is>
+      </c>
+      <c r="K19" s="18" t="inlineStr">
+        <is>
+          <t>Fixed 2026-08-17. Root cause of Decision B non-advance in Tracole E2E. 2 lines + 1 regression test. 10 pytest pass in 2.83s (test_we_stage_version_init.py 2/2 plus 8 other WE tests). Live verified against founder-os-58/Tracole tenant: broken workflow healed + advanced, post-fix inserts correct, engine gate refuses non-owner as designed.</t>
+        </is>
+      </c>
+      <c r="L19" s="18" t="inlineStr">
+        <is>
+          <t>Founder review 2026-08-17 (post-compaction session)</t>
         </is>
       </c>
     </row>
